--- a/tests/Metrado.Excel.Tests/Goldens/mixed-units.xlsx
+++ b/tests/Metrado.Excel.Tests/Goldens/mixed-units.xlsx
@@ -39,6 +39,12 @@
   </x:si>
   <x:si>
     <x:t>Boundary mode</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Material</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Layers</x:t>
   </x:si>
   <x:si>
     <x:t>CAPITULO</x:t>
@@ -461,10 +467,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G15"/>
+  <x:dimension ref="A1:I15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
+    <x:row r="1" spans="1:9">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -472,7 +478,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:7">
+    <x:row r="2" spans="1:9">
       <x:c r="A2" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -494,247 +500,253 @@
       <x:c r="G2" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
+      <x:c r="H2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9">
       <x:c r="A3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:7">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:9">
       <x:c r="A5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9">
+      <x:c r="A6" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9">
+      <x:c r="A7" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:7">
-      <x:c r="A7" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>14.2</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:7">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
       <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>14.2</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:7">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9">
       <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>14.2</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:7">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>19.75</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:9">
+      <x:c r="A12" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" spans="1:7">
-      <x:c r="A12" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>12.5</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:9">
+      <x:c r="A13" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:7">
-      <x:c r="A13" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>7.25</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:9">
+      <x:c r="A14" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:7">
-      <x:c r="A14" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:7">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -751,34 +763,37 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D3"/>
+  <x:dimension ref="A1:E3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:4">
+    <x:row r="1" spans="1:5">
       <x:c r="A1" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:4">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5">
       <x:c r="A2" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B2" s="0">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:4">
+    <x:row r="3" spans="1:5">
       <x:c r="A3" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/tests/Metrado.Excel.Tests/Goldens/mixed-units.xlsx
+++ b/tests/Metrado.Excel.Tests/Goldens/mixed-units.xlsx
@@ -104,7 +104,7 @@
     <x:t>walls-03</x:t>
   </x:si>
   <x:si>
-    <x:t>Unclassified elements</x:t>
+    <x:t>Unclassified lines</x:t>
   </x:si>
   <x:si>
     <x:t>Count</x:t>
